--- a/clean/chemistry/chem_water_analysis_2024.xlsx
+++ b/clean/chemistry/chem_water_analysis_2024.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data'!$A$1:$BF$250</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data'!$A$1:$BH$250</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF250"/>
+  <dimension ref="A1:BH250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -502,6 +502,8 @@
     <col width="27" customWidth="1" min="56" max="56"/>
     <col width="15" customWidth="1" min="57" max="57"/>
     <col width="33" customWidth="1" min="58" max="58"/>
+    <col width="29" customWidth="1" min="59" max="59"/>
+    <col width="17" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -795,6 +797,16 @@
           <t>sample_name_group</t>
         </is>
       </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>sector_flag</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -921,6 +933,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1047,6 +1064,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1173,6 +1195,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1299,6 +1326,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1425,6 +1457,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1551,6 +1588,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1677,6 +1719,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1803,6 +1850,11 @@
           <t>مياة معبأة</t>
         </is>
       </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1929,6 +1981,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2055,6 +2112,11 @@
           <t>موية</t>
         </is>
       </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2182,6 +2244,11 @@
           <t>موية براده</t>
         </is>
       </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2308,6 +2375,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2434,6 +2506,11 @@
           <t>موية غسيل</t>
         </is>
       </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2560,6 +2637,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2686,6 +2768,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2812,6 +2899,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2938,6 +3030,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3064,6 +3161,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3190,6 +3292,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3316,6 +3423,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3442,6 +3554,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3568,6 +3685,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3694,6 +3816,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3820,6 +3947,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3946,6 +4078,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4072,6 +4209,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG27" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4198,6 +4340,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG28" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4324,6 +4471,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG29" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4450,6 +4602,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG30" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4621,6 +4778,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG31" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4792,6 +4954,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG32" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4963,6 +5130,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG33" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5134,6 +5306,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG34" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5305,6 +5482,11 @@
           <t>المياه</t>
         </is>
       </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5476,6 +5658,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG36" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5647,6 +5834,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG37" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5818,6 +6010,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG38" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5994,6 +6191,11 @@
           <t>ماء غسيل</t>
         </is>
       </c>
+      <c r="BG39" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6165,6 +6367,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG40" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6336,6 +6543,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG41" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6507,6 +6719,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG42" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6678,6 +6895,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG43" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6849,6 +7071,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG44" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7020,6 +7247,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG45" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7191,6 +7423,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG46" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7362,6 +7599,11 @@
           <t>المياه</t>
         </is>
       </c>
+      <c r="BG47" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7538,6 +7780,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG48" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7714,6 +7961,11 @@
           <t>المياه</t>
         </is>
       </c>
+      <c r="BG49" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7885,6 +8137,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG50" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الجنوب</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8056,6 +8313,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG51" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8227,6 +8489,11 @@
           <t>المياه</t>
         </is>
       </c>
+      <c r="BG52" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8398,6 +8665,11 @@
           <t>مياه غسيل</t>
         </is>
       </c>
+      <c r="BG53" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8569,6 +8841,11 @@
           <t>مياه غسيل</t>
         </is>
       </c>
+      <c r="BG54" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8740,6 +9017,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG55" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8911,6 +9193,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG56" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9082,6 +9369,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG57" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9253,6 +9545,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG58" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9424,6 +9721,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG59" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9595,6 +9897,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG60" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9771,6 +10078,11 @@
           <t>مياة معبأة تانيا</t>
         </is>
       </c>
+      <c r="BG61" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9942,6 +10254,11 @@
           <t>مياه غسيل عامل</t>
         </is>
       </c>
+      <c r="BG62" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -10113,6 +10430,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG63" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -10289,6 +10611,11 @@
           <t>عينة خاصة</t>
         </is>
       </c>
+      <c r="BH64" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10455,6 +10782,11 @@
           <t>مياه غسيل ١</t>
         </is>
       </c>
+      <c r="BG65" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10626,6 +10958,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG66" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -10797,6 +11134,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG67" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10968,6 +11310,11 @@
           <t>مياه غسيل ١</t>
         </is>
       </c>
+      <c r="BG68" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -11139,6 +11486,11 @@
           <t>مياه غسيل ٢</t>
         </is>
       </c>
+      <c r="BG69" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -11310,6 +11662,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG70" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -11481,6 +11838,11 @@
           <t>مياه غسيل</t>
         </is>
       </c>
+      <c r="BG71" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -11652,6 +12014,11 @@
           <t>مياه غسيل الارز</t>
         </is>
       </c>
+      <c r="BG72" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -11828,6 +12195,11 @@
           <t>مياه غسيل</t>
         </is>
       </c>
+      <c r="BG73" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -11999,6 +12371,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG74" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -12170,6 +12547,11 @@
           <t>مياه غسيل</t>
         </is>
       </c>
+      <c r="BG75" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشمال</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -12341,6 +12723,11 @@
           <t>مياه غسيل</t>
         </is>
       </c>
+      <c r="BG76" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -12512,6 +12899,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG77" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -12683,6 +13075,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG78" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -12854,6 +13251,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG79" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -13025,6 +13427,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG80" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -13196,6 +13603,11 @@
           <t>مياة غسيل</t>
         </is>
       </c>
+      <c r="BG81" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -13367,6 +13779,11 @@
           <t>مياة غسيل</t>
         </is>
       </c>
+      <c r="BG82" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -13543,6 +13960,11 @@
           <t>مياة طبخ</t>
         </is>
       </c>
+      <c r="BG83" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -13714,6 +14136,11 @@
           <t>مياة غسيل</t>
         </is>
       </c>
+      <c r="BG84" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -13890,6 +14317,11 @@
           <t>مياة العجانة</t>
         </is>
       </c>
+      <c r="BG85" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -14061,6 +14493,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG86" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -14232,6 +14669,11 @@
           <t>مياه غسيل ادوات</t>
         </is>
       </c>
+      <c r="BG87" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -14403,6 +14845,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG88" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -14574,6 +15021,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG89" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -14745,6 +15197,11 @@
           <t>مياة سخان</t>
         </is>
       </c>
+      <c r="BG90" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -14916,6 +15373,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG91" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -15087,6 +15549,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG92" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -15263,6 +15730,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG93" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -15434,6 +15906,11 @@
           <t>مياة معبأة</t>
         </is>
       </c>
+      <c r="BG94" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -15605,6 +16082,11 @@
           <t>مياة غسيل</t>
         </is>
       </c>
+      <c r="BG95" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -15776,6 +16258,11 @@
           <t>مياة غسيل الاسماك</t>
         </is>
       </c>
+      <c r="BG96" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -15947,6 +16434,11 @@
           <t>مياة معبأة</t>
         </is>
       </c>
+      <c r="BG97" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -16118,6 +16610,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG98" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -16289,6 +16786,11 @@
           <t>مياة غسيل الاسماك</t>
         </is>
       </c>
+      <c r="BG99" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -16460,6 +16962,11 @@
           <t>مياه غسيل الاسماك</t>
         </is>
       </c>
+      <c r="BG100" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -16636,6 +17143,11 @@
           <t>مياه غسيل داوات</t>
         </is>
       </c>
+      <c r="BG101" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -16807,6 +17319,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG102" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -16978,6 +17495,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG103" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -17149,6 +17671,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG104" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -17320,6 +17847,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG105" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -17491,6 +18023,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG106" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -17662,6 +18199,11 @@
           <t>مياة غسيل حنفية</t>
         </is>
       </c>
+      <c r="BG107" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -17833,6 +18375,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG108" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -18004,6 +18551,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG109" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -18175,6 +18727,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG110" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -18351,6 +18908,11 @@
           <t>مياة حنفية للطبخ</t>
         </is>
       </c>
+      <c r="BG111" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -18527,6 +19089,11 @@
           <t>مياة غسيل الارز و ادوات التحضير</t>
         </is>
       </c>
+      <c r="BG112" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -18698,6 +19265,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG113" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -18869,6 +19441,11 @@
           <t>مياة حنفية</t>
         </is>
       </c>
+      <c r="BG114" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -19040,6 +19617,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG115" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -19211,6 +19793,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG116" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -19382,6 +19969,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG117" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -19553,6 +20145,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG118" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -19734,6 +20331,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG119" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -19905,6 +20507,11 @@
           <t>مياة حنفية للطبخ</t>
         </is>
       </c>
+      <c r="BG120" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -20076,6 +20683,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG121" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -20257,6 +20869,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG122" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -20428,6 +21045,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG123" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -20599,6 +21221,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG124" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -20780,6 +21407,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG125" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -20961,6 +21593,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG126" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -21142,6 +21779,11 @@
           <t>مياة حنفية لغسيل الادوات ١</t>
         </is>
       </c>
+      <c r="BG127" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -21323,6 +21965,11 @@
           <t>مياة حنفية لغسيل الادوات ٢</t>
         </is>
       </c>
+      <c r="BG128" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -21494,6 +22141,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG129" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -21675,6 +22327,11 @@
           <t>مياة حنفية لغسيل الادوات ١</t>
         </is>
       </c>
+      <c r="BG130" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -21856,6 +22513,11 @@
           <t>مياه حنفية لغسيل الادوات ٢</t>
         </is>
       </c>
+      <c r="BG131" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -22037,6 +22699,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG132" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -22218,6 +22885,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG133" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -22399,6 +23071,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG134" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -22570,6 +23247,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG135" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -22751,6 +23433,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG136" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -22922,6 +23609,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG137" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -23093,6 +23785,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG138" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -23264,6 +23961,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG139" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -23435,6 +24137,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG140" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -23606,6 +24313,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG141" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -23777,6 +24489,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG142" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -23948,6 +24665,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG143" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -24119,6 +24841,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG144" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -24290,6 +25017,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG145" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -24461,6 +25193,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG146" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -24632,6 +25369,11 @@
           <t>مياه حنفية للعجانة</t>
         </is>
       </c>
+      <c r="BG147" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -24813,6 +25555,11 @@
           <t>مياه غسيل الاسماك</t>
         </is>
       </c>
+      <c r="BG148" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -24994,6 +25741,11 @@
           <t>مياه حنفية غسيل ادوات</t>
         </is>
       </c>
+      <c r="BG149" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -25165,6 +25917,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG150" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -25336,6 +26093,11 @@
           <t>مياة حنفية لغسيل الأدوات</t>
         </is>
       </c>
+      <c r="BG151" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -25507,6 +26269,11 @@
           <t>مياة حنفية لغسيل الأدوات(1)</t>
         </is>
       </c>
+      <c r="BG152" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -25678,6 +26445,11 @@
           <t>مياة حنفية لغسيل الأدوات(2)</t>
         </is>
       </c>
+      <c r="BG153" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -25849,6 +26621,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG154" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -26020,6 +26797,11 @@
           <t>مياة حنفية غسيل</t>
         </is>
       </c>
+      <c r="BG155" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -26191,6 +26973,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG156" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -26362,6 +27149,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG157" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -26533,6 +27325,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG158" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -26704,6 +27501,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG159" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -26875,6 +27677,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG160" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -27046,6 +27853,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG161" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -27222,6 +28034,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG162" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -27393,6 +28210,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG163" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -27564,6 +28386,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG164" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -27735,6 +28562,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG165" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -27911,6 +28743,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG166" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -28082,6 +28919,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG167" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -28253,6 +29095,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG168" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -28424,6 +29271,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG169" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -28595,6 +29447,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG170" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -28766,6 +29623,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG171" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -28942,6 +29804,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG172" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -29118,6 +29985,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG173" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -29294,6 +30166,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG174" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -29465,6 +30342,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG175" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -29636,6 +30518,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG176" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -29807,6 +30694,11 @@
           <t>مياة حنفية</t>
         </is>
       </c>
+      <c r="BG177" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -29978,6 +30870,11 @@
           <t>مياة حنفية لغسيل الارز</t>
         </is>
       </c>
+      <c r="BG178" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -30149,6 +31046,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG179" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -30320,6 +31222,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG180" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -30491,6 +31398,11 @@
           <t>مياة معبأة للطبخ</t>
         </is>
       </c>
+      <c r="BG181" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -30667,6 +31579,11 @@
           <t>مياة معبأة للعجانة</t>
         </is>
       </c>
+      <c r="BG182" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -30838,6 +31755,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG183" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -31009,6 +31931,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG184" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -31180,6 +32107,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG185" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -31351,6 +32283,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG186" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -31522,6 +32459,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG187" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -31693,6 +32635,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG188" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -31864,6 +32811,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG189" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -32035,6 +32987,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG190" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -32206,6 +33163,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG191" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -32377,6 +33339,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="BG192" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -32548,6 +33515,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG193" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -32719,6 +33691,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG194" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -32890,6 +33867,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG195" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -33061,6 +34043,11 @@
           <t>مياه غسيل أدوات</t>
         </is>
       </c>
+      <c r="BG196" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -33232,6 +34219,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG197" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -33408,6 +34400,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG198" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -33579,6 +34576,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG199" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -33750,6 +34752,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG200" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -33921,6 +34928,11 @@
           <t>مياة حنفية لغسيل الادوات - ك</t>
         </is>
       </c>
+      <c r="BG201" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -34092,6 +35104,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG202" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -34268,6 +35285,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG203" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -34444,6 +35466,11 @@
           <t>A مياة</t>
         </is>
       </c>
+      <c r="BH204" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -34620,6 +35647,11 @@
           <t>B مياة</t>
         </is>
       </c>
+      <c r="BH205" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -34796,6 +35828,11 @@
           <t>C مياة</t>
         </is>
       </c>
+      <c r="BH206" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -34967,6 +36004,11 @@
           <t>مياة حنفية للطبخ م.ك</t>
         </is>
       </c>
+      <c r="BG207" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -35138,6 +36180,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG208" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -35309,6 +36356,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG209" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -35480,6 +36532,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG210" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -35651,6 +36708,11 @@
           <t>مياة حنفية لغسيل الادوات م.ك</t>
         </is>
       </c>
+      <c r="BG211" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -35822,6 +36884,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG212" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -35993,6 +37060,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG213" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -36164,6 +37236,11 @@
           <t>مياة معبأة للطبخ م.ك</t>
         </is>
       </c>
+      <c r="BG214" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -36335,6 +37412,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG215" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -36506,6 +37588,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG216" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -36677,6 +37764,11 @@
           <t>موية غسيل ادوات</t>
         </is>
       </c>
+      <c r="BG217" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -36853,6 +37945,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG218" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -37024,6 +38121,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG219" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -37195,6 +38297,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG220" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -37371,6 +38478,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG221" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -37542,6 +38654,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG222" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -37713,6 +38830,11 @@
           <t>مياة حنفية للغسيل م.ك</t>
         </is>
       </c>
+      <c r="BG223" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -37884,6 +39006,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG224" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -38055,6 +39182,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG225" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -38226,6 +39358,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG226" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -38397,6 +39534,11 @@
           <t>مياة حنفية للغسيل م.ك</t>
         </is>
       </c>
+      <c r="BG227" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -38568,6 +39710,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BG228" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -38734,6 +39881,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH229" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -38900,6 +40052,11 @@
           <t>مياة حنفية لغسيل الادوات م.ك</t>
         </is>
       </c>
+      <c r="BH230" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -39066,6 +40223,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH231" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -39232,6 +40394,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH232" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -39398,6 +40565,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH233" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -39564,6 +40736,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH234" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -39730,6 +40907,11 @@
           <t>مياة حنفية للغسيل م.ك</t>
         </is>
       </c>
+      <c r="BH235" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -39896,6 +41078,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH236" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -40062,6 +41249,11 @@
           <t>مياة حنفية للغسيل م.ك</t>
         </is>
       </c>
+      <c r="BH237" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -40228,6 +41420,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH238" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -40394,6 +41591,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH239" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -40560,6 +41762,11 @@
           <t>مياة حنفية م.ك</t>
         </is>
       </c>
+      <c r="BH240" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -40726,6 +41933,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="BH241" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -40897,6 +42109,11 @@
           <t>مياة حنفية لغسيل الاسماك م.ك</t>
         </is>
       </c>
+      <c r="BH242" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -41063,6 +42280,11 @@
           <t>مياة حنفية لغسيل الادوات م.ك</t>
         </is>
       </c>
+      <c r="BH243" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -41229,6 +42451,11 @@
           <t>مياةحنفية للغسيل م.ك</t>
         </is>
       </c>
+      <c r="BH244" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -41377,6 +42604,11 @@
           <t>defaulted</t>
         </is>
       </c>
+      <c r="BH245" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -41530,6 +42762,11 @@
           <t>defaulted</t>
         </is>
       </c>
+      <c r="BH246" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -41678,6 +42915,11 @@
           <t>defaulted</t>
         </is>
       </c>
+      <c r="BH247" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -41823,6 +43065,11 @@
           <t>defaulted</t>
         </is>
       </c>
+      <c r="BH248" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -41976,6 +43223,11 @@
           <t>defaulted</t>
         </is>
       </c>
+      <c r="BH249" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -42115,9 +43367,14 @@
           <t>defaulted</t>
         </is>
       </c>
+      <c r="BH250" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BF250"/>
+  <autoFilter ref="A1:BH250"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -42128,7 +43385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -42154,7 +43411,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Columns: 58</t>
+          <t>Columns: 60</t>
         </is>
       </c>
     </row>
@@ -43189,6 +44446,42 @@
       <c r="D63" t="inlineStr">
         <is>
           <t>مياه فلتر | مياه فلتر | مياه فلتر</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>223</v>
+      </c>
+      <c r="C64" t="n">
+        <v>26</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق | فرع أمانة في الشرق | فرع أمانة في الشرق</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>sector_flag</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>26</v>
+      </c>
+      <c r="C65" t="n">
+        <v>223</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>no_municipality | private | private</t>
         </is>
       </c>
     </row>

--- a/clean/chemistry/chem_water_analysis_2024.xlsx
+++ b/clean/chemistry/chem_water_analysis_2024.xlsx
@@ -1842,7 +1842,7 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -6181,11 +6181,6 @@
           <t>مياه الحنفية</t>
         </is>
       </c>
-      <c r="BE39" t="inlineStr">
-        <is>
-          <t>defaulted</t>
-        </is>
-      </c>
       <c r="BF39" t="inlineStr">
         <is>
           <t>ماء غسيل</t>
@@ -10070,7 +10065,7 @@
       </c>
       <c r="BD61" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF61" t="inlineStr">
@@ -10598,7 +10593,7 @@
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>أغذية متنوعة</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
@@ -15898,7 +15893,7 @@
       </c>
       <c r="BD94" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF94" t="inlineStr">
@@ -16426,7 +16421,7 @@
       </c>
       <c r="BD97" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF97" t="inlineStr">
@@ -31390,7 +31385,7 @@
       </c>
       <c r="BD181" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF181" t="inlineStr">
@@ -31571,7 +31566,7 @@
       </c>
       <c r="BD182" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF182" t="inlineStr">
@@ -37228,7 +37223,7 @@
       </c>
       <c r="BD214" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF214" t="inlineStr">
@@ -42599,11 +42594,6 @@
           <t>مياه الحنفية</t>
         </is>
       </c>
-      <c r="BE245" t="inlineStr">
-        <is>
-          <t>defaulted</t>
-        </is>
-      </c>
       <c r="BH245" t="inlineStr">
         <is>
           <t>no_municipality</t>
@@ -42757,11 +42747,6 @@
           <t>مياه الحنفية</t>
         </is>
       </c>
-      <c r="BE246" t="inlineStr">
-        <is>
-          <t>defaulted</t>
-        </is>
-      </c>
       <c r="BH246" t="inlineStr">
         <is>
           <t>no_municipality</t>
@@ -42910,11 +42895,6 @@
           <t>مياه الحنفية</t>
         </is>
       </c>
-      <c r="BE247" t="inlineStr">
-        <is>
-          <t>defaulted</t>
-        </is>
-      </c>
       <c r="BH247" t="inlineStr">
         <is>
           <t>no_municipality</t>
@@ -43060,11 +43040,6 @@
           <t>مياه الحنفية</t>
         </is>
       </c>
-      <c r="BE248" t="inlineStr">
-        <is>
-          <t>defaulted</t>
-        </is>
-      </c>
       <c r="BH248" t="inlineStr">
         <is>
           <t>no_municipality</t>
@@ -43218,11 +43193,6 @@
           <t>مياه الحنفية</t>
         </is>
       </c>
-      <c r="BE249" t="inlineStr">
-        <is>
-          <t>defaulted</t>
-        </is>
-      </c>
       <c r="BH249" t="inlineStr">
         <is>
           <t>no_municipality</t>
@@ -43360,11 +43330,6 @@
       <c r="BD250" t="inlineStr">
         <is>
           <t>مياه الحنفية</t>
-        </is>
-      </c>
-      <c r="BE250" t="inlineStr">
-        <is>
-          <t>defaulted</t>
         </is>
       </c>
       <c r="BH250" t="inlineStr">
@@ -44420,14 +44385,14 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>defaulted | defaulted | defaulted</t>
+          <t>defaulted</t>
         </is>
       </c>
     </row>

--- a/clean/chemistry/chem_water_analysis_2024.xlsx
+++ b/clean/chemistry/chem_water_analysis_2024.xlsx
@@ -1711,7 +1711,7 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
@@ -34387,7 +34387,7 @@
       </c>
       <c r="BD198" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BF198" t="inlineStr">
@@ -42744,7 +42744,7 @@
       </c>
       <c r="BD246" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="BH246" t="inlineStr">

--- a/clean/chemistry/chem_water_analysis_2024.xlsx
+++ b/clean/chemistry/chem_water_analysis_2024.xlsx
@@ -10593,7 +10593,7 @@
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>أغذية متنوعة</t>
+          <t>أخرى</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">

--- a/clean/chemistry/chem_water_analysis_2024.xlsx
+++ b/clean/chemistry/chem_water_analysis_2024.xlsx
@@ -1711,7 +1711,7 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه الحنفية</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه الحنفية</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه الحنفية</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه الحنفية</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه الحنفية</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">

--- a/clean/chemistry/chem_water_analysis_2024.xlsx
+++ b/clean/chemistry/chem_water_analysis_2024.xlsx
@@ -925,7 +925,7 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="BD40" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF40" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="BD41" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF41" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF43" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="BD47" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF47" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF51" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF52" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF54" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF55" t="inlineStr">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="BD58" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF58" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="BD59" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF59" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="BD60" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF60" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="BD61" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF61" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BD62" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="BD63" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="BD65" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF65" t="inlineStr">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="BD66" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF66" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="BD67" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF67" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="BD68" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF68" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF70" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF71" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="BD72" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF72" t="inlineStr">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="BD74" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF74" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="BD75" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF75" t="inlineStr">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="BD76" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF76" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="BD80" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF80" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="BD81" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF81" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="BD82" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF82" t="inlineStr">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="BD83" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF83" t="inlineStr">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="BD84" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF84" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="BD85" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF85" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="BD86" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF86" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="BD87" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF87" t="inlineStr">
@@ -14832,7 +14832,7 @@
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
@@ -15008,7 +15008,7 @@
       </c>
       <c r="BD89" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF89" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="BD90" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF90" t="inlineStr">
@@ -15360,7 +15360,7 @@
       </c>
       <c r="BD91" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF91" t="inlineStr">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="BD92" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF92" t="inlineStr">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="BD93" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF93" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="BD94" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF94" t="inlineStr">
@@ -16069,7 +16069,7 @@
       </c>
       <c r="BD95" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF95" t="inlineStr">
@@ -16245,7 +16245,7 @@
       </c>
       <c r="BD96" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF96" t="inlineStr">
@@ -16421,7 +16421,7 @@
       </c>
       <c r="BD97" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF97" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="BD98" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF98" t="inlineStr">
@@ -16773,7 +16773,7 @@
       </c>
       <c r="BD99" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF99" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="BD100" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF100" t="inlineStr">
@@ -17130,7 +17130,7 @@
       </c>
       <c r="BD101" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF101" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="BD102" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF102" t="inlineStr">
@@ -17482,7 +17482,7 @@
       </c>
       <c r="BD103" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF103" t="inlineStr">
@@ -17658,7 +17658,7 @@
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
@@ -17834,7 +17834,7 @@
       </c>
       <c r="BD105" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF105" t="inlineStr">
@@ -18010,7 +18010,7 @@
       </c>
       <c r="BD106" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF106" t="inlineStr">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BD107" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF107" t="inlineStr">
@@ -18362,7 +18362,7 @@
       </c>
       <c r="BD108" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF108" t="inlineStr">
@@ -18538,7 +18538,7 @@
       </c>
       <c r="BD109" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF109" t="inlineStr">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="BD110" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF110" t="inlineStr">
@@ -18895,7 +18895,7 @@
       </c>
       <c r="BD111" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF111" t="inlineStr">
@@ -19076,7 +19076,7 @@
       </c>
       <c r="BD112" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF112" t="inlineStr">
@@ -19252,7 +19252,7 @@
       </c>
       <c r="BD113" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF113" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="BD114" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF114" t="inlineStr">
@@ -19604,7 +19604,7 @@
       </c>
       <c r="BD115" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF115" t="inlineStr">
@@ -19780,7 +19780,7 @@
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
@@ -19956,7 +19956,7 @@
       </c>
       <c r="BD117" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF117" t="inlineStr">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="BD118" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF118" t="inlineStr">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="BD119" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF119" t="inlineStr">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="BD120" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF120" t="inlineStr">
@@ -20670,7 +20670,7 @@
       </c>
       <c r="BD121" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF121" t="inlineStr">
@@ -20856,7 +20856,7 @@
       </c>
       <c r="BD122" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF122" t="inlineStr">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="BD123" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF123" t="inlineStr">
@@ -21208,7 +21208,7 @@
       </c>
       <c r="BD124" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF124" t="inlineStr">
@@ -21394,7 +21394,7 @@
       </c>
       <c r="BD125" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF125" t="inlineStr">
@@ -21580,7 +21580,7 @@
       </c>
       <c r="BD126" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF126" t="inlineStr">
@@ -21766,7 +21766,7 @@
       </c>
       <c r="BD127" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF127" t="inlineStr">
@@ -21952,7 +21952,7 @@
       </c>
       <c r="BD128" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF128" t="inlineStr">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
@@ -22314,7 +22314,7 @@
       </c>
       <c r="BD130" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF130" t="inlineStr">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
@@ -22686,7 +22686,7 @@
       </c>
       <c r="BD132" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF132" t="inlineStr">
@@ -22872,7 +22872,7 @@
       </c>
       <c r="BD133" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF133" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="BD134" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF134" t="inlineStr">
@@ -23234,7 +23234,7 @@
       </c>
       <c r="BD135" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF135" t="inlineStr">
@@ -23420,7 +23420,7 @@
       </c>
       <c r="BD136" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF136" t="inlineStr">
@@ -23596,7 +23596,7 @@
       </c>
       <c r="BD137" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF137" t="inlineStr">
@@ -23772,7 +23772,7 @@
       </c>
       <c r="BD138" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF138" t="inlineStr">
@@ -23948,7 +23948,7 @@
       </c>
       <c r="BD139" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF139" t="inlineStr">
@@ -24124,7 +24124,7 @@
       </c>
       <c r="BD140" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF140" t="inlineStr">
@@ -24300,7 +24300,7 @@
       </c>
       <c r="BD141" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF141" t="inlineStr">
@@ -24476,7 +24476,7 @@
       </c>
       <c r="BD142" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF142" t="inlineStr">
@@ -24652,7 +24652,7 @@
       </c>
       <c r="BD143" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF143" t="inlineStr">
@@ -24828,7 +24828,7 @@
       </c>
       <c r="BD144" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF144" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
@@ -25180,7 +25180,7 @@
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
@@ -25356,7 +25356,7 @@
       </c>
       <c r="BD147" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF147" t="inlineStr">
@@ -25542,7 +25542,7 @@
       </c>
       <c r="BD148" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF148" t="inlineStr">
@@ -25728,7 +25728,7 @@
       </c>
       <c r="BD149" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF149" t="inlineStr">
@@ -25904,7 +25904,7 @@
       </c>
       <c r="BD150" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF150" t="inlineStr">
@@ -26080,7 +26080,7 @@
       </c>
       <c r="BD151" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF151" t="inlineStr">
@@ -26256,7 +26256,7 @@
       </c>
       <c r="BD152" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF152" t="inlineStr">
@@ -26432,7 +26432,7 @@
       </c>
       <c r="BD153" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF153" t="inlineStr">
@@ -26608,7 +26608,7 @@
       </c>
       <c r="BD154" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF154" t="inlineStr">
@@ -26784,7 +26784,7 @@
       </c>
       <c r="BD155" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF155" t="inlineStr">
@@ -26960,7 +26960,7 @@
       </c>
       <c r="BD156" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF156" t="inlineStr">
@@ -27136,7 +27136,7 @@
       </c>
       <c r="BD157" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF157" t="inlineStr">
@@ -27312,7 +27312,7 @@
       </c>
       <c r="BD158" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF158" t="inlineStr">
@@ -27488,7 +27488,7 @@
       </c>
       <c r="BD159" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF159" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="BD160" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF160" t="inlineStr">
@@ -27840,7 +27840,7 @@
       </c>
       <c r="BD161" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF161" t="inlineStr">
@@ -28021,7 +28021,7 @@
       </c>
       <c r="BD162" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF162" t="inlineStr">
@@ -28197,7 +28197,7 @@
       </c>
       <c r="BD163" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF163" t="inlineStr">
@@ -28373,7 +28373,7 @@
       </c>
       <c r="BD164" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF164" t="inlineStr">
@@ -28549,7 +28549,7 @@
       </c>
       <c r="BD165" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF165" t="inlineStr">
@@ -28730,7 +28730,7 @@
       </c>
       <c r="BD166" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF166" t="inlineStr">
@@ -28906,7 +28906,7 @@
       </c>
       <c r="BD167" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF167" t="inlineStr">
@@ -29082,7 +29082,7 @@
       </c>
       <c r="BD168" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF168" t="inlineStr">
@@ -29258,7 +29258,7 @@
       </c>
       <c r="BD169" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF169" t="inlineStr">
@@ -29434,7 +29434,7 @@
       </c>
       <c r="BD170" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF170" t="inlineStr">
@@ -29610,7 +29610,7 @@
       </c>
       <c r="BD171" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF171" t="inlineStr">
@@ -29791,7 +29791,7 @@
       </c>
       <c r="BD172" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF172" t="inlineStr">
@@ -29972,7 +29972,7 @@
       </c>
       <c r="BD173" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF173" t="inlineStr">
@@ -30153,7 +30153,7 @@
       </c>
       <c r="BD174" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF174" t="inlineStr">
@@ -30329,7 +30329,7 @@
       </c>
       <c r="BD175" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF175" t="inlineStr">
@@ -30505,7 +30505,7 @@
       </c>
       <c r="BD176" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF176" t="inlineStr">
@@ -30681,7 +30681,7 @@
       </c>
       <c r="BD177" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF177" t="inlineStr">
@@ -30857,7 +30857,7 @@
       </c>
       <c r="BD178" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF178" t="inlineStr">
@@ -31033,7 +31033,7 @@
       </c>
       <c r="BD179" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF179" t="inlineStr">
@@ -31209,7 +31209,7 @@
       </c>
       <c r="BD180" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF180" t="inlineStr">
@@ -31385,7 +31385,7 @@
       </c>
       <c r="BD181" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF181" t="inlineStr">
@@ -31566,7 +31566,7 @@
       </c>
       <c r="BD182" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF182" t="inlineStr">
@@ -31742,7 +31742,7 @@
       </c>
       <c r="BD183" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF183" t="inlineStr">
@@ -31918,7 +31918,7 @@
       </c>
       <c r="BD184" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF184" t="inlineStr">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="BD185" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF185" t="inlineStr">
@@ -32270,7 +32270,7 @@
       </c>
       <c r="BD186" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF186" t="inlineStr">
@@ -32446,7 +32446,7 @@
       </c>
       <c r="BD187" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF187" t="inlineStr">
@@ -32622,7 +32622,7 @@
       </c>
       <c r="BD188" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF188" t="inlineStr">
@@ -32798,7 +32798,7 @@
       </c>
       <c r="BD189" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF189" t="inlineStr">
@@ -32974,7 +32974,7 @@
       </c>
       <c r="BD190" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF190" t="inlineStr">
@@ -33150,7 +33150,7 @@
       </c>
       <c r="BD191" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF191" t="inlineStr">
@@ -33326,7 +33326,7 @@
       </c>
       <c r="BD192" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF192" t="inlineStr">
@@ -33502,7 +33502,7 @@
       </c>
       <c r="BD193" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF193" t="inlineStr">
@@ -33678,7 +33678,7 @@
       </c>
       <c r="BD194" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF194" t="inlineStr">
@@ -33854,7 +33854,7 @@
       </c>
       <c r="BD195" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF195" t="inlineStr">
@@ -34030,7 +34030,7 @@
       </c>
       <c r="BD196" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF196" t="inlineStr">
@@ -34206,7 +34206,7 @@
       </c>
       <c r="BD197" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF197" t="inlineStr">
@@ -34387,7 +34387,7 @@
       </c>
       <c r="BD198" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF198" t="inlineStr">
@@ -34563,7 +34563,7 @@
       </c>
       <c r="BD199" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF199" t="inlineStr">
@@ -34739,7 +34739,7 @@
       </c>
       <c r="BD200" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF200" t="inlineStr">
@@ -34915,7 +34915,7 @@
       </c>
       <c r="BD201" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF201" t="inlineStr">
@@ -35091,7 +35091,7 @@
       </c>
       <c r="BD202" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF202" t="inlineStr">
@@ -35272,7 +35272,7 @@
       </c>
       <c r="BD203" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF203" t="inlineStr">
@@ -35453,7 +35453,7 @@
       </c>
       <c r="BD204" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF204" t="inlineStr">
@@ -35634,7 +35634,7 @@
       </c>
       <c r="BD205" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF205" t="inlineStr">
@@ -35815,7 +35815,7 @@
       </c>
       <c r="BD206" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF206" t="inlineStr">
@@ -35991,7 +35991,7 @@
       </c>
       <c r="BD207" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF207" t="inlineStr">
@@ -36167,7 +36167,7 @@
       </c>
       <c r="BD208" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF208" t="inlineStr">
@@ -36343,7 +36343,7 @@
       </c>
       <c r="BD209" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF209" t="inlineStr">
@@ -36519,7 +36519,7 @@
       </c>
       <c r="BD210" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF210" t="inlineStr">
@@ -36695,7 +36695,7 @@
       </c>
       <c r="BD211" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF211" t="inlineStr">
@@ -36871,7 +36871,7 @@
       </c>
       <c r="BD212" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF212" t="inlineStr">
@@ -37047,7 +37047,7 @@
       </c>
       <c r="BD213" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF213" t="inlineStr">
@@ -37223,7 +37223,7 @@
       </c>
       <c r="BD214" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF214" t="inlineStr">
@@ -37399,7 +37399,7 @@
       </c>
       <c r="BD215" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF215" t="inlineStr">
@@ -37575,7 +37575,7 @@
       </c>
       <c r="BD216" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF216" t="inlineStr">
@@ -37751,7 +37751,7 @@
       </c>
       <c r="BD217" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF217" t="inlineStr">
@@ -37932,7 +37932,7 @@
       </c>
       <c r="BD218" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF218" t="inlineStr">
@@ -38108,7 +38108,7 @@
       </c>
       <c r="BD219" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF219" t="inlineStr">
@@ -38284,7 +38284,7 @@
       </c>
       <c r="BD220" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF220" t="inlineStr">
@@ -38465,7 +38465,7 @@
       </c>
       <c r="BD221" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF221" t="inlineStr">
@@ -38641,7 +38641,7 @@
       </c>
       <c r="BD222" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF222" t="inlineStr">
@@ -38817,7 +38817,7 @@
       </c>
       <c r="BD223" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF223" t="inlineStr">
@@ -38993,7 +38993,7 @@
       </c>
       <c r="BD224" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF224" t="inlineStr">
@@ -39169,7 +39169,7 @@
       </c>
       <c r="BD225" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF225" t="inlineStr">
@@ -39345,7 +39345,7 @@
       </c>
       <c r="BD226" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF226" t="inlineStr">
@@ -39521,7 +39521,7 @@
       </c>
       <c r="BD227" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF227" t="inlineStr">
@@ -39697,7 +39697,7 @@
       </c>
       <c r="BD228" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF228" t="inlineStr">
@@ -39868,7 +39868,7 @@
       </c>
       <c r="BD229" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF229" t="inlineStr">
@@ -40039,7 +40039,7 @@
       </c>
       <c r="BD230" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF230" t="inlineStr">
@@ -40210,7 +40210,7 @@
       </c>
       <c r="BD231" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF231" t="inlineStr">
@@ -40381,7 +40381,7 @@
       </c>
       <c r="BD232" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF232" t="inlineStr">
@@ -40552,7 +40552,7 @@
       </c>
       <c r="BD233" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF233" t="inlineStr">
@@ -40723,7 +40723,7 @@
       </c>
       <c r="BD234" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF234" t="inlineStr">
@@ -40894,7 +40894,7 @@
       </c>
       <c r="BD235" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF235" t="inlineStr">
@@ -41065,7 +41065,7 @@
       </c>
       <c r="BD236" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF236" t="inlineStr">
@@ -41236,7 +41236,7 @@
       </c>
       <c r="BD237" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF237" t="inlineStr">
@@ -41407,7 +41407,7 @@
       </c>
       <c r="BD238" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF238" t="inlineStr">
@@ -41578,7 +41578,7 @@
       </c>
       <c r="BD239" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF239" t="inlineStr">
@@ -41749,7 +41749,7 @@
       </c>
       <c r="BD240" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF240" t="inlineStr">
@@ -41920,7 +41920,7 @@
       </c>
       <c r="BD241" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF241" t="inlineStr">
@@ -42096,7 +42096,7 @@
       </c>
       <c r="BD242" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF242" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="BD243" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF243" t="inlineStr">
@@ -42438,7 +42438,7 @@
       </c>
       <c r="BD244" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BF244" t="inlineStr">
@@ -42591,7 +42591,7 @@
       </c>
       <c r="BD245" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BH245" t="inlineStr">
@@ -42744,7 +42744,7 @@
       </c>
       <c r="BD246" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BH246" t="inlineStr">
@@ -42892,7 +42892,7 @@
       </c>
       <c r="BD247" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BH247" t="inlineStr">
@@ -43037,7 +43037,7 @@
       </c>
       <c r="BD248" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BH248" t="inlineStr">
@@ -43190,7 +43190,7 @@
       </c>
       <c r="BD249" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BH249" t="inlineStr">
@@ -43329,7 +43329,7 @@
       </c>
       <c r="BD250" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BH250" t="inlineStr">
@@ -44374,7 +44374,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>مياه فلتر | مياه فلتر | مياه فلتر</t>
+          <t>مياه صالحة للشرب | مياه صالحة للشرب | مياه صالحة للشرب</t>
         </is>
       </c>
     </row>

--- a/clean/chemistry/chem_water_analysis_2024.xlsx
+++ b/clean/chemistry/chem_water_analysis_2024.xlsx
@@ -10593,7 +10593,7 @@
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>أخرى</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
